--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1452"/>
+  <dimension ref="A1:I1456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -48124,8 +48124,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1444" t="n">
-        <v/>
+      <c r="F1444" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1444" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1445">
@@ -48152,8 +48157,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1445" t="n">
-        <v/>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1445" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1446">
@@ -48180,8 +48190,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1446" t="n">
-        <v/>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1446" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1447">
@@ -48208,8 +48223,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1447" t="n">
-        <v/>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1447" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1448">
@@ -48236,8 +48256,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1448" t="n">
-        <v/>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1448" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1449">
@@ -48264,8 +48289,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1449" t="n">
-        <v/>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1449" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1450">
@@ -48292,8 +48322,13 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1450" t="n">
-        <v/>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1450" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1451">
@@ -48320,8 +48355,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1451" t="n">
-        <v/>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="G1451" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1452">
@@ -48348,7 +48388,124 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1452" t="n">
+      <c r="F1452" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1452" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="n">
+        <v>1023080</v>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>Sun, Sep 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1453" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="n">
+        <v>1023079</v>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>Sun, Sep 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="F1454" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="n">
+        <v>1023077</v>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>Sun, Sep 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1455" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="n">
+        <v>1023078</v>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>Sun, Sep 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="F1456" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1456"/>
+  <dimension ref="A1:I1461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -48421,8 +48421,13 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1453" t="n">
-        <v/>
+      <c r="F1453" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1453" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1454">
@@ -48449,8 +48454,13 @@
           <t>Wenatchee Wild</t>
         </is>
       </c>
-      <c r="F1454" t="n">
-        <v/>
+      <c r="F1454" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="G1454" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1455">
@@ -48477,8 +48487,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1455" t="n">
-        <v/>
+      <c r="F1455" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1455" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1456">
@@ -48505,7 +48520,152 @@
           <t>Kamloops Blazers</t>
         </is>
       </c>
-      <c r="F1456" t="n">
+      <c r="F1456" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1456" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="n">
+        <v>1023081</v>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>Fri, Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1457" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="n">
+        <v>1023082</v>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>Fri, Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1458" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="n">
+        <v>1023083</v>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>Fri, Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1459" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="n">
+        <v>1023084</v>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>Fri, Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1460" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="n">
+        <v>1023085</v>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>Fri, Sep 18, 2026</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1461" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1461"/>
+  <dimension ref="A1:I1471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -48553,8 +48553,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1457" t="n">
-        <v/>
+      <c r="F1457" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1457" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1458">
@@ -48581,8 +48586,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1458" t="n">
-        <v/>
+      <c r="F1458" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1458" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1459">
@@ -48609,8 +48619,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1459" t="n">
-        <v/>
+      <c r="F1459" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1459" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1460">
@@ -48637,8 +48652,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1460" t="n">
-        <v/>
+      <c r="F1460" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1460" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1461">
@@ -48665,7 +48685,292 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1461" t="n">
+      <c r="F1461" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1461" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="n">
+        <v>1023089</v>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>Sat, Sep 19, 2026</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1462" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="n">
+        <v>1023091</v>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>Sat, Sep 19, 2026</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1463" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="n">
+        <v>1023092</v>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>Sat, Sep 19, 2026</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1464" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="n">
+        <v>1023087</v>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>Sat, Sep 19, 2026</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1465" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="n">
+        <v>1023088</v>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>Sat, Sep 19, 2026</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1466" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="n">
+        <v>1023090</v>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>Sat, Sep 19, 2026</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1467" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="n">
+        <v>1023095</v>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>Sat, Sep 19, 2026</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1468" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="n">
+        <v>1023086</v>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>Sat, Sep 19, 2026</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1469" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="n">
+        <v>1023093</v>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>Sat, Sep 19, 2026</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1470" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="n">
+        <v>1023094</v>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>Sat, Sep 19, 2026</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="F1471" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1471"/>
+  <dimension ref="A1:I1472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -48718,8 +48718,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1462" t="n">
-        <v/>
+      <c r="F1462" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="G1462" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1463">
@@ -48746,8 +48751,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1463" t="n">
-        <v/>
+      <c r="F1463" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1463" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1464">
@@ -48774,8 +48784,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1464" t="n">
-        <v/>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1464" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1465">
@@ -48802,8 +48817,13 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1465" t="n">
-        <v/>
+      <c r="F1465" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="G1465" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1466">
@@ -48830,8 +48850,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1466" t="n">
-        <v/>
+      <c r="F1466" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1466" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1467">
@@ -48858,8 +48883,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1467" t="n">
-        <v/>
+      <c r="F1467" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1467" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1468">
@@ -48886,8 +48916,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1468" t="n">
-        <v/>
+      <c r="F1468" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1468" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1469">
@@ -48914,8 +48949,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1469" t="n">
-        <v/>
+      <c r="F1469" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="G1469" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1470">
@@ -48942,8 +48982,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1470" t="n">
-        <v/>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1470" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1471">
@@ -48970,7 +49015,40 @@
           <t>Vancouver Giants</t>
         </is>
       </c>
-      <c r="F1471" t="n">
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1471" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="n">
+        <v>1023096</v>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>Sun, Sep 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1472" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1472"/>
+  <dimension ref="A1:I1480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -49048,7 +49048,236 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1472" t="n">
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1472" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="n">
+        <v>1023097</v>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>Fri, Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1473" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="n">
+        <v>1023098</v>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>Fri, Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1474" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="n">
+        <v>1023100</v>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>Fri, Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="F1475" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="n">
+        <v>1023102</v>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>Fri, Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1476" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="n">
+        <v>1023103</v>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>Fri, Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="F1477" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="n">
+        <v>1023099</v>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>Fri, Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1478" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="n">
+        <v>1023101</v>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>Fri, Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1479" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="n">
+        <v>1023104</v>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>Fri, Sep 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="F1480" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1480"/>
+  <dimension ref="A1:I1489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -49081,8 +49081,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1473" t="n">
-        <v/>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1473" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1474">
@@ -49109,8 +49114,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1474" t="n">
-        <v/>
+      <c r="F1474" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1474" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1475">
@@ -49137,8 +49147,13 @@
           <t>Red Deer Rebels</t>
         </is>
       </c>
-      <c r="F1475" t="n">
-        <v/>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1475" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1476">
@@ -49165,8 +49180,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1476" t="n">
-        <v/>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1476" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1477">
@@ -49193,8 +49213,13 @@
           <t>Swift Current Broncos</t>
         </is>
       </c>
-      <c r="F1477" t="n">
-        <v/>
+      <c r="F1477" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1477" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1478">
@@ -49221,8 +49246,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1478" t="n">
-        <v/>
+      <c r="F1478" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1478" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1479">
@@ -49249,8 +49279,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1479" t="n">
-        <v/>
+      <c r="F1479" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1479" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1480">
@@ -49277,7 +49312,264 @@
           <t>Kamloops Blazers</t>
         </is>
       </c>
-      <c r="F1480" t="n">
+      <c r="F1480" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1480" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="n">
+        <v>1023106</v>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>Sat, Sep 26, 2026</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1481" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="n">
+        <v>1023108</v>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>Sat, Sep 26, 2026</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1482" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="n">
+        <v>1023107</v>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>Sat, Sep 26, 2026</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="F1483" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="n">
+        <v>1023109</v>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>Sat, Sep 26, 2026</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1484" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="n">
+        <v>1023113</v>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>Sat, Sep 26, 2026</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1485" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="n">
+        <v>1023105</v>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>Sat, Sep 26, 2026</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1486" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="n">
+        <v>1023110</v>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>Sat, Sep 26, 2026</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1487" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="n">
+        <v>1023111</v>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>Sat, Sep 26, 2026</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1488" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="n">
+        <v>1023112</v>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>Sat, Sep 26, 2026</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="F1489" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1489"/>
+  <dimension ref="A1:I1492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -49345,8 +49345,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1481" t="n">
-        <v/>
+      <c r="F1481" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="G1481" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1482">
@@ -49373,8 +49378,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1482" t="n">
-        <v/>
+      <c r="F1482" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1482" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1483">
@@ -49401,8 +49411,13 @@
           <t>Kamloops Blazers</t>
         </is>
       </c>
-      <c r="F1483" t="n">
-        <v/>
+      <c r="F1483" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="G1483" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1484">
@@ -49429,8 +49444,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1484" t="n">
-        <v/>
+      <c r="F1484" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1484" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1485">
@@ -49457,8 +49477,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1485" t="n">
-        <v/>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1485" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1486">
@@ -49485,8 +49510,13 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1486" t="n">
-        <v/>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1486" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1487">
@@ -49513,8 +49543,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1487" t="n">
-        <v/>
+      <c r="F1487" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1487" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1488">
@@ -49541,8 +49576,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1488" t="n">
-        <v/>
+      <c r="F1488" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1488" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1489">
@@ -49569,7 +49609,96 @@
           <t>Vancouver Giants</t>
         </is>
       </c>
-      <c r="F1489" t="n">
+      <c r="F1489" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="G1489" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="n">
+        <v>1023115</v>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>Sun, Sep 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1490" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="n">
+        <v>1023114</v>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>Sun, Sep 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1491" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="n">
+        <v>1023116</v>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>Sun, Sep 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="F1492" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1492"/>
+  <dimension ref="A1:I1493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -49642,8 +49642,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1490" t="n">
-        <v/>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1490" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1491">
@@ -49670,8 +49675,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1491" t="n">
-        <v/>
+      <c r="F1491" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1491" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1492">
@@ -49698,7 +49708,40 @@
           <t>Vancouver Giants</t>
         </is>
       </c>
-      <c r="F1492" t="n">
+      <c r="F1492" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1492" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="n">
+        <v>1023117</v>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>Wed, Sep 30, 2026</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1493" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1493"/>
+  <dimension ref="A1:I1502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -49741,7 +49741,264 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1493" t="n">
+      <c r="F1493" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1493" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="n">
+        <v>1023118</v>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>Fri, Oct 2, 2026</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1494" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="n">
+        <v>1023120</v>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>Fri, Oct 2, 2026</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1495" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="n">
+        <v>1023124</v>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>Fri, Oct 2, 2026</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1496" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="n">
+        <v>1023122</v>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>Fri, Oct 2, 2026</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1497" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="n">
+        <v>1023123</v>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>Fri, Oct 2, 2026</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1498" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="n">
+        <v>1023119</v>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>Fri, Oct 2, 2026</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1499" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="n">
+        <v>1023121</v>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>Fri, Oct 2, 2026</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="F1500" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="n">
+        <v>1023125</v>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>Fri, Oct 2, 2026</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1501" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="n">
+        <v>1023126</v>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>Fri, Oct 2, 2026</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1502" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1502"/>
+  <dimension ref="A1:I1510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -49774,8 +49774,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1494" t="n">
-        <v/>
+      <c r="F1494" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1494" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1495">
@@ -49802,8 +49807,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1495" t="n">
-        <v/>
+      <c r="F1495" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="G1495" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1496">
@@ -49830,8 +49840,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1496" t="n">
-        <v/>
+      <c r="F1496" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1496" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1497">
@@ -49858,8 +49873,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1497" t="n">
-        <v/>
+      <c r="F1497" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1497" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1498">
@@ -49886,8 +49906,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1498" t="n">
-        <v/>
+      <c r="F1498" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1498" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1499">
@@ -49914,8 +49939,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1499" t="n">
-        <v/>
+      <c r="F1499" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1499" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1500">
@@ -49942,8 +49972,13 @@
           <t>Vancouver Giants</t>
         </is>
       </c>
-      <c r="F1500" t="n">
-        <v/>
+      <c r="F1500" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1500" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1501">
@@ -49970,8 +50005,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1501" t="n">
-        <v/>
+      <c r="F1501" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="G1501" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1502">
@@ -49998,7 +50038,236 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1502" t="n">
+      <c r="F1502" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="G1502" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="n">
+        <v>1023129</v>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>Sat, Oct 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1503" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="n">
+        <v>1023131</v>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>Sat, Oct 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="F1504" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="n">
+        <v>1023128</v>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>Sat, Oct 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1505" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="n">
+        <v>1023130</v>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>Sat, Oct 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1506" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="n">
+        <v>1023133</v>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>Sat, Oct 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1507" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="n">
+        <v>1023127</v>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>Sat, Oct 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1508" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="n">
+        <v>1023132</v>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>Sat, Oct 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="F1509" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="n">
+        <v>1023134</v>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>Sat, Oct 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="F1510" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1510"/>
+  <dimension ref="A1:I1513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -50071,8 +50071,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1503" t="n">
-        <v/>
+      <c r="F1503" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1503" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1504">
@@ -50099,8 +50104,13 @@
           <t>Red Deer Rebels</t>
         </is>
       </c>
-      <c r="F1504" t="n">
-        <v/>
+      <c r="F1504" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1504" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1505">
@@ -50127,8 +50137,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1505" t="n">
-        <v/>
+      <c r="F1505" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1505" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1506">
@@ -50155,8 +50170,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1506" t="n">
-        <v/>
+      <c r="F1506" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1506" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1507">
@@ -50183,8 +50203,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1507" t="n">
-        <v/>
+      <c r="F1507" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1507" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1508">
@@ -50211,8 +50236,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1508" t="n">
-        <v/>
+      <c r="F1508" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="G1508" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1509">
@@ -50239,8 +50269,13 @@
           <t>Tri-City Americans</t>
         </is>
       </c>
-      <c r="F1509" t="n">
-        <v/>
+      <c r="F1509" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1509" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1510">
@@ -50267,7 +50302,96 @@
           <t>Vancouver Giants</t>
         </is>
       </c>
-      <c r="F1510" t="n">
+      <c r="F1510" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1510" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="n">
+        <v>1023135</v>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>Sun, Oct 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1511" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="n">
+        <v>1023136</v>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>Sun, Oct 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1512" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="n">
+        <v>1023137</v>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>Sun, Oct 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1513" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1513"/>
+  <dimension ref="A1:I1515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -50335,8 +50335,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1511" t="n">
-        <v/>
+      <c r="F1511" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1511" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1512">
@@ -50363,8 +50368,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1512" t="n">
-        <v/>
+      <c r="F1512" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1512" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1513">
@@ -50391,7 +50401,68 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1513" t="n">
+      <c r="F1513" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1513" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="n">
+        <v>1023138</v>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>Tue, Oct 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1514" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="n">
+        <v>1023139</v>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>Tue, Oct 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1515" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1515"/>
+  <dimension ref="A1:I1518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -50434,8 +50434,13 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1514" t="n">
-        <v/>
+      <c r="F1514" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1514" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1515">
@@ -50462,7 +50467,96 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1515" t="n">
+      <c r="F1515" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1515" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="n">
+        <v>1023140</v>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>Wed, Oct 7, 2026</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1516" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="n">
+        <v>1023141</v>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>Wed, Oct 7, 2026</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1517" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="n">
+        <v>1023142</v>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>Wed, Oct 7, 2026</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="F1518" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1518"/>
+  <dimension ref="A1:I1528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -50500,8 +50500,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1516" t="n">
-        <v/>
+      <c r="F1516" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1516" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1517">
@@ -50528,8 +50533,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1517" t="n">
-        <v/>
+      <c r="F1517" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1517" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1518">
@@ -50556,7 +50566,292 @@
           <t>Lethbridge Hurricanes</t>
         </is>
       </c>
-      <c r="F1518" t="n">
+      <c r="F1518" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="G1518" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="n">
+        <v>1023144</v>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>Fri, Oct 9, 2026</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1519" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="n">
+        <v>1023147</v>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>Fri, Oct 9, 2026</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1520" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="n">
+        <v>1023148</v>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>Fri, Oct 9, 2026</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1521" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="n">
+        <v>1023149</v>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>Fri, Oct 9, 2026</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1522" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="n">
+        <v>1023143</v>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>Fri, Oct 9, 2026</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="F1523" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="n">
+        <v>1023146</v>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>Fri, Oct 9, 2026</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="F1524" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="n">
+        <v>1023145</v>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>Fri, Oct 9, 2026</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1525" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="n">
+        <v>1023150</v>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>Fri, Oct 9, 2026</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1526" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1526" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="n">
+        <v>1023151</v>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>Fri, Oct 9, 2026</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1527" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1527" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="n">
+        <v>1023152</v>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>Fri, Oct 9, 2026</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1528" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1528" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1528"/>
+  <dimension ref="A1:I1536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -50599,8 +50599,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1519" t="n">
-        <v/>
+      <c r="F1519" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1519" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1520">
@@ -50627,8 +50632,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1520" t="n">
-        <v/>
+      <c r="F1520" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1520" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1521">
@@ -50655,8 +50665,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1521" t="n">
-        <v/>
+      <c r="F1521" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1521" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1522">
@@ -50683,8 +50698,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1522" t="n">
-        <v/>
+      <c r="F1522" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1522" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1523">
@@ -50711,8 +50731,13 @@
           <t>Swift Current Broncos</t>
         </is>
       </c>
-      <c r="F1523" t="n">
-        <v/>
+      <c r="F1523" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1523" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1524">
@@ -50739,8 +50764,13 @@
           <t>Portland Winterhawks</t>
         </is>
       </c>
-      <c r="F1524" t="n">
-        <v/>
+      <c r="F1524" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="G1524" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1525">
@@ -50767,8 +50797,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1525" t="n">
-        <v/>
+      <c r="F1525" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1525" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1526">
@@ -50795,8 +50830,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1526" t="n">
-        <v/>
+      <c r="F1526" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1526" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1527">
@@ -50823,8 +50863,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1527" t="n">
-        <v/>
+      <c r="F1527" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="G1527" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1528">
@@ -50851,7 +50896,236 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1528" t="n">
+      <c r="F1528" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="G1528" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="n">
+        <v>1023155</v>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>Sat, Oct 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1529" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1529" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="n">
+        <v>1023154</v>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>Sat, Oct 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1530" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="n">
+        <v>1023156</v>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>Sat, Oct 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1531" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1531" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="n">
+        <v>1023160</v>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>Sat, Oct 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1532" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="F1532" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="n">
+        <v>1023153</v>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>Sat, Oct 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1533" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1533" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="n">
+        <v>1023157</v>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>Sat, Oct 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1534" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="n">
+        <v>1023158</v>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>Sat, Oct 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1535" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="n">
+        <v>1023159</v>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>Sat, Oct 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1536" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1536" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1536"/>
+  <dimension ref="A1:I1538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -50929,8 +50929,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1529" t="n">
-        <v/>
+      <c r="F1529" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="G1529" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1530">
@@ -50957,8 +50962,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1530" t="n">
-        <v/>
+      <c r="F1530" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="G1530" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1531">
@@ -50985,8 +50995,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1531" t="n">
-        <v/>
+      <c r="F1531" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1531" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1532">
@@ -51013,8 +51028,13 @@
           <t>Lethbridge Hurricanes</t>
         </is>
       </c>
-      <c r="F1532" t="n">
-        <v/>
+      <c r="F1532" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="G1532" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1533">
@@ -51041,8 +51061,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1533" t="n">
-        <v/>
+      <c r="F1533" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1533" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1534">
@@ -51069,8 +51094,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1534" t="n">
-        <v/>
+      <c r="F1534" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1534" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1535">
@@ -51097,8 +51127,13 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1535" t="n">
-        <v/>
+      <c r="F1535" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="G1535" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1536">
@@ -51125,7 +51160,68 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1536" t="n">
+      <c r="F1536" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1536" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="n">
+        <v>1023161</v>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>Sun, Oct 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1537" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="F1537" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="n">
+        <v>1023162</v>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>Sun, Oct 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1538" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="F1538" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1538"/>
+  <dimension ref="A1:I1541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -51193,8 +51193,13 @@
           <t>Swift Current Broncos</t>
         </is>
       </c>
-      <c r="F1537" t="n">
-        <v/>
+      <c r="F1537" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1537" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1538">
@@ -51221,7 +51226,96 @@
           <t>Tri-City Americans</t>
         </is>
       </c>
-      <c r="F1538" t="n">
+      <c r="F1538" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="G1538" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="n">
+        <v>1023163</v>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>Mon, Oct 12, 2026</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1539" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1539" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="n">
+        <v>1023165</v>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>Mon, Oct 12, 2026</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="F1540" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="n">
+        <v>1023164</v>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>Mon, Oct 12, 2026</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1541" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="F1541" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1541"/>
+  <dimension ref="A1:I1543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -51259,8 +51259,13 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1539" t="n">
-        <v/>
+      <c r="F1539" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="G1539" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1540">
@@ -51287,8 +51292,13 @@
           <t>Red Deer Rebels</t>
         </is>
       </c>
-      <c r="F1540" t="n">
-        <v/>
+      <c r="F1540" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1540" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1541">
@@ -51315,7 +51325,68 @@
           <t>Portland Winterhawks</t>
         </is>
       </c>
-      <c r="F1541" t="n">
+      <c r="F1541" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1541" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="n">
+        <v>1023166</v>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>Tue, Oct 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1542" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1542" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="n">
+        <v>1023167</v>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>Tue, Oct 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1543" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1543" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1543"/>
+  <dimension ref="A1:I1545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -51358,8 +51358,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1542" t="n">
-        <v/>
+      <c r="F1542" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1542" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1543">
@@ -51386,7 +51391,68 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1543" t="n">
+      <c r="F1543" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1543" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="n">
+        <v>1023168</v>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>Wed, Oct 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1544" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1544" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="n">
+        <v>1023169</v>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>Wed, Oct 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1545" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="F1545" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1545"/>
+  <dimension ref="A1:I1554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -51424,8 +51424,13 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1544" t="n">
-        <v/>
+      <c r="F1544" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="G1544" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1545">
@@ -51452,7 +51457,264 @@
           <t>Portland Winterhawks</t>
         </is>
       </c>
-      <c r="F1545" t="n">
+      <c r="F1545" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="G1545" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="n">
+        <v>1023170</v>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>Fri, Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1546" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1546" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="n">
+        <v>1023172</v>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>Fri, Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1547" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="F1547" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="n">
+        <v>1023173</v>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>Fri, Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1548" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="F1548" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="n">
+        <v>1023174</v>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>Fri, Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1549" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1549" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="n">
+        <v>1023176</v>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>Fri, Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1550" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1550" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="n">
+        <v>1023178</v>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>Fri, Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1551" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="n">
+        <v>1023171</v>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>Fri, Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1552" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="n">
+        <v>1023175</v>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>Fri, Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1553" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1553" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="n">
+        <v>1023177</v>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>Fri, Oct 16, 2026</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1554" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="F1554" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1554"/>
+  <dimension ref="A1:I1564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -51490,8 +51490,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1546" t="n">
-        <v/>
+      <c r="F1546" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="G1546" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1547">
@@ -51518,8 +51523,13 @@
           <t>Moose Jaw Warriors</t>
         </is>
       </c>
-      <c r="F1547" t="n">
-        <v/>
+      <c r="F1547" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="G1547" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1548">
@@ -51546,8 +51556,13 @@
           <t>Red Deer Rebels</t>
         </is>
       </c>
-      <c r="F1548" t="n">
-        <v/>
+      <c r="F1548" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1548" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1549">
@@ -51574,8 +51589,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1549" t="n">
-        <v/>
+      <c r="F1549" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1549" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1550">
@@ -51602,8 +51622,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1550" t="n">
-        <v/>
+      <c r="F1550" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1550" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1551">
@@ -51630,8 +51655,13 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1551" t="n">
-        <v/>
+      <c r="F1551" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="G1551" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1552">
@@ -51658,8 +51688,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1552" t="n">
-        <v/>
+      <c r="F1552" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1552" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1553">
@@ -51686,8 +51721,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1553" t="n">
-        <v/>
+      <c r="F1553" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1553" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1554">
@@ -51714,7 +51754,292 @@
           <t>Tri-City Americans</t>
         </is>
       </c>
-      <c r="F1554" t="n">
+      <c r="F1554" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1554" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="n">
+        <v>1023180</v>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>Sat, Oct 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1555" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="F1555" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="n">
+        <v>1023179</v>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>Sat, Oct 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1556" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="n">
+        <v>1023182</v>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>Sat, Oct 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1557" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1557" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="n">
+        <v>1023186</v>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>Sat, Oct 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1558" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1558" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="n">
+        <v>1023184</v>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>Sat, Oct 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1559" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1559" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="n">
+        <v>1023188</v>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>Sat, Oct 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="F1560" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="n">
+        <v>1023181</v>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>Sat, Oct 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1561" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1561" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="n">
+        <v>1023183</v>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>Sat, Oct 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1562" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="F1562" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="n">
+        <v>1023185</v>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>Sat, Oct 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1563" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1563" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="n">
+        <v>1023187</v>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>Sat, Oct 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1564" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1564" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1564"/>
+  <dimension ref="A1:I1566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -51787,8 +51787,13 @@
           <t>Red Deer Rebels</t>
         </is>
       </c>
-      <c r="F1555" t="n">
-        <v/>
+      <c r="F1555" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1555" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1556">
@@ -51815,8 +51820,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1556" t="n">
-        <v/>
+      <c r="F1556" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1556" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1557">
@@ -51843,8 +51853,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1557" t="n">
-        <v/>
+      <c r="F1557" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1557" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1558">
@@ -51871,8 +51886,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1558" t="n">
-        <v/>
+      <c r="F1558" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1558" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1559">
@@ -51899,8 +51919,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1559" t="n">
-        <v/>
+      <c r="F1559" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1559" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1560">
@@ -51927,8 +51952,13 @@
           <t>Kamloops Blazers</t>
         </is>
       </c>
-      <c r="F1560" t="n">
-        <v/>
+      <c r="F1560" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1560" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1561">
@@ -51955,8 +51985,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1561" t="n">
-        <v/>
+      <c r="F1561" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1561" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1562">
@@ -51983,8 +52018,13 @@
           <t>Vancouver Giants</t>
         </is>
       </c>
-      <c r="F1562" t="n">
-        <v/>
+      <c r="F1562" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1562" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1563">
@@ -52011,8 +52051,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1563" t="n">
-        <v/>
+      <c r="F1563" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1563" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1564">
@@ -52039,7 +52084,68 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1564" t="n">
+      <c r="F1564" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="G1564" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="n">
+        <v>1023189</v>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>Sun, Oct 18, 2026</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1565" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1565" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="n">
+        <v>1023190</v>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>Sun, Oct 18, 2026</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1566" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1566" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1566"/>
+  <dimension ref="A1:I1568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -52117,8 +52117,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1565" t="n">
-        <v/>
+      <c r="F1565" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1565" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1566">
@@ -52145,7 +52150,68 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1566" t="n">
+      <c r="F1566" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1566" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="n">
+        <v>1023191</v>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>Tue, Oct 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1567" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="F1567" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="n">
+        <v>1023192</v>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>Tue, Oct 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1568" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="F1568" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1568"/>
+  <dimension ref="A1:I1574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -52183,8 +52183,13 @@
           <t>Swift Current Broncos</t>
         </is>
       </c>
-      <c r="F1567" t="n">
-        <v/>
+      <c r="F1567" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1567" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1568">
@@ -52211,7 +52216,180 @@
           <t>Vancouver Giants</t>
         </is>
       </c>
-      <c r="F1568" t="n">
+      <c r="F1568" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1568" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="n">
+        <v>1023198</v>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>Wed, Oct 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1569" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1569" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="n">
+        <v>1023193</v>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>Wed, Oct 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1570" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1570" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="n">
+        <v>1023197</v>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>Wed, Oct 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1571" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1571" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="n">
+        <v>1023194</v>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>Wed, Oct 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1572" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="F1572" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="n">
+        <v>1023196</v>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>Wed, Oct 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1573" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="F1573" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="n">
+        <v>1023195</v>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>Wed, Oct 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1574" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1574" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1574"/>
+  <dimension ref="A1:I1585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -52249,8 +52249,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1569" t="n">
-        <v/>
+      <c r="F1569" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1569" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1570">
@@ -52277,8 +52282,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1570" t="n">
-        <v/>
+      <c r="F1570" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1570" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1571">
@@ -52305,8 +52315,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1571" t="n">
-        <v/>
+      <c r="F1571" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1571" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1572">
@@ -52333,8 +52348,13 @@
           <t>Tri-City Americans</t>
         </is>
       </c>
-      <c r="F1572" t="n">
-        <v/>
+      <c r="F1572" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1572" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1573">
@@ -52361,8 +52381,13 @@
           <t>Vancouver Giants</t>
         </is>
       </c>
-      <c r="F1573" t="n">
-        <v/>
+      <c r="F1573" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1573" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1574">
@@ -52389,7 +52414,320 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1574" t="n">
+      <c r="F1574" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="G1574" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="n">
+        <v>1023199</v>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>Fri, Oct 23, 2026</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1575" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1575" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="n">
+        <v>1023200</v>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>Fri, Oct 23, 2026</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1576" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="n">
+        <v>1023201</v>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>Fri, Oct 23, 2026</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1577" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="n">
+        <v>1023203</v>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>Fri, Oct 23, 2026</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="F1578" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="n">
+        <v>1023204</v>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>Fri, Oct 23, 2026</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1579" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="n">
+        <v>1023206</v>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>Fri, Oct 23, 2026</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="F1580" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="n">
+        <v>1023207</v>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>Fri, Oct 23, 2026</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1581" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="n">
+        <v>1023202</v>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>Fri, Oct 23, 2026</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="F1582" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="n">
+        <v>1023205</v>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>Fri, Oct 23, 2026</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="F1583" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="n">
+        <v>1023208</v>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>Fri, Oct 23, 2026</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1584" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="n">
+        <v>1023209</v>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>Fri, Oct 23, 2026</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1585" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1585"/>
+  <dimension ref="A1:I1592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -52447,8 +52447,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1575" t="n">
-        <v/>
+      <c r="F1575" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1575" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1576">
@@ -52475,8 +52480,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1576" t="n">
-        <v/>
+      <c r="F1576" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1576" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1577">
@@ -52503,8 +52513,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1577" t="n">
-        <v/>
+      <c r="F1577" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1577" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1578">
@@ -52531,8 +52546,13 @@
           <t>Lethbridge Hurricanes</t>
         </is>
       </c>
-      <c r="F1578" t="n">
-        <v/>
+      <c r="F1578" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1578" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1579">
@@ -52559,8 +52579,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1579" t="n">
-        <v/>
+      <c r="F1579" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1579" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1580">
@@ -52587,8 +52612,13 @@
           <t>Red Deer Rebels</t>
         </is>
       </c>
-      <c r="F1580" t="n">
-        <v/>
+      <c r="F1580" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1580" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1581">
@@ -52615,8 +52645,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1581" t="n">
-        <v/>
+      <c r="F1581" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1581" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1582">
@@ -52643,8 +52678,13 @@
           <t>Vancouver Giants</t>
         </is>
       </c>
-      <c r="F1582" t="n">
-        <v/>
+      <c r="F1582" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1582" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1583">
@@ -52671,8 +52711,13 @@
           <t>Tri-City Americans</t>
         </is>
       </c>
-      <c r="F1583" t="n">
-        <v/>
+      <c r="F1583" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="G1583" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1584">
@@ -52699,8 +52744,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1584" t="n">
-        <v/>
+      <c r="F1584" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1584" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1585">
@@ -52727,7 +52777,208 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1585" t="n">
+      <c r="F1585" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="G1585" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="n">
+        <v>1023216</v>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>Sat, Oct 24, 2026</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1586" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="n">
+        <v>1023211</v>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>Sat, Oct 24, 2026</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1587" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1587" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="n">
+        <v>1023213</v>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>Sat, Oct 24, 2026</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1588" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="F1588" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="n">
+        <v>1023215</v>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>Sat, Oct 24, 2026</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1589" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1589" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="n">
+        <v>1023210</v>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>Sat, Oct 24, 2026</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1590" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="n">
+        <v>1023212</v>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>Sat, Oct 24, 2026</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="F1591" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="n">
+        <v>1023214</v>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>Sat, Oct 24, 2026</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1592" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1592"/>
+  <dimension ref="A1:I1596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -52810,8 +52810,13 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1586" t="n">
-        <v/>
+      <c r="F1586" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="G1586" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1587">
@@ -52838,8 +52843,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1587" t="n">
-        <v/>
+      <c r="F1587" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1587" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1588">
@@ -52866,8 +52876,13 @@
           <t>Red Deer Rebels</t>
         </is>
       </c>
-      <c r="F1588" t="n">
-        <v/>
+      <c r="F1588" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="G1588" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1589">
@@ -52894,8 +52909,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1589" t="n">
-        <v/>
+      <c r="F1589" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1589" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1590">
@@ -52922,8 +52942,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1590" t="n">
-        <v/>
+      <c r="F1590" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1590" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1591">
@@ -52950,8 +52975,13 @@
           <t>Tri-City Americans</t>
         </is>
       </c>
-      <c r="F1591" t="n">
-        <v/>
+      <c r="F1591" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="G1591" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1592">
@@ -52978,7 +53008,124 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1592" t="n">
+      <c r="F1592" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1592" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="n">
+        <v>1023217</v>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>Sun, Oct 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1593" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="n">
+        <v>1023218</v>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>Sun, Oct 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1594" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="n">
+        <v>1023219</v>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>Sun, Oct 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1595" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1595" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="n">
+        <v>1023220</v>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>Sun, Oct 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1596" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="F1596" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1596"/>
+  <dimension ref="A1:I1599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -53041,8 +53041,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1593" t="n">
-        <v/>
+      <c r="F1593" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1593" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1594">
@@ -53069,8 +53074,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1594" t="n">
-        <v/>
+      <c r="F1594" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1594" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1595">
@@ -53097,8 +53107,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1595" t="n">
-        <v/>
+      <c r="F1595" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1595" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1596">
@@ -53125,7 +53140,96 @@
           <t>Kamloops Blazers</t>
         </is>
       </c>
-      <c r="F1596" t="n">
+      <c r="F1596" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="G1596" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="n">
+        <v>1023221</v>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>Tue, Oct 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1597" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1597" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="n">
+        <v>1023222</v>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>Tue, Oct 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1598" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="n">
+        <v>1023223</v>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>Tue, Oct 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1599" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1599" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1599"/>
+  <dimension ref="A1:I1603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -53173,8 +53173,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1597" t="n">
-        <v/>
+      <c r="F1597" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1597" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1598">
@@ -53201,8 +53206,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1598" t="n">
-        <v/>
+      <c r="F1598" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1598" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1599">
@@ -53229,7 +53239,124 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1599" t="n">
+      <c r="F1599" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1599" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="n">
+        <v>1023225</v>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>Wed, Oct 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1600" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1600" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="n">
+        <v>1023226</v>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>Wed, Oct 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1601" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1601" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="n">
+        <v>1023227</v>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>Wed, Oct 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1602" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1602" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="n">
+        <v>1023224</v>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>Wed, Oct 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1603" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="F1603" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1603"/>
+  <dimension ref="A1:I1612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -53272,8 +53272,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1600" t="n">
-        <v/>
+      <c r="F1600" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1600" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1601">
@@ -53300,8 +53305,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1601" t="n">
-        <v/>
+      <c r="F1601" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1601" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1602">
@@ -53328,8 +53338,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1602" t="n">
-        <v/>
+      <c r="F1602" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="G1602" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1603">
@@ -53356,7 +53371,264 @@
           <t>Vancouver Giants</t>
         </is>
       </c>
-      <c r="F1603" t="n">
+      <c r="F1603" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="G1603" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="n">
+        <v>1023228</v>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>Fri, Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1604" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1604" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="n">
+        <v>1023229</v>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>Fri, Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1605" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1605" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="n">
+        <v>1023231</v>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>Fri, Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1606" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1606" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="n">
+        <v>1023232</v>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>Fri, Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1607" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="F1607" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="n">
+        <v>1023234</v>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>Fri, Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1608" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="F1608" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="n">
+        <v>1023235</v>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>Fri, Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1609" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1609" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="n">
+        <v>1023236</v>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>Fri, Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1610" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="F1610" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="n">
+        <v>1023230</v>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>Fri, Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1611" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="F1611" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="n">
+        <v>1023233</v>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>Fri, Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1612" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1612" t="n">
         <v/>
       </c>
     </row>
